--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
@@ -476,41 +476,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
+          <t>{'mlp__activation': 'identity', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (15, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7035</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9724</v>
+        <v>0.9932</v>
       </c>
       <c r="E2" t="n">
-        <v>21.9188</v>
+        <v>8.812900000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.73      0.97      0.83        99
-           1       0.53      0.31      0.39       104
-           2       0.55      0.65      0.60       112
-           3       0.75      0.93      0.83        86
-           4       0.72      0.73      0.72        88
-           5       0.74      0.60      0.66        98
-           6       0.84      0.91      0.88       101
-           7       0.73      0.59      0.65        94
-           8       0.73      0.68      0.70        99
-           9       0.95      1.00      0.98       105
-          10       0.60      0.76      0.67       121
-          11       0.51      0.39      0.45        99
-          12       0.85      0.73      0.79        94
-          13       0.84      0.97      0.90        97
-          14       0.39      0.22      0.28       102
-          15       0.78      0.74      0.76        91
-          16       0.60      0.82      0.69       110
-    accuracy                           0.70      1700
-   macro avg       0.70      0.71      0.69      1700
-weighted avg       0.69      0.70      0.69      1700
+           0       0.99      0.99      0.99        99
+           1       0.60      0.82      0.69       104
+           2       0.96      0.97      0.97       112
+           3       0.95      1.00      0.97        86
+           4       0.90      0.95      0.93        88
+           5       0.92      0.95      0.93        98
+           6       0.82      0.86      0.84       101
+           7       0.96      0.70      0.81        94
+           8       0.84      0.85      0.84        99
+           9       0.99      1.00      1.00       105
+          10       0.93      0.79      0.85       121
+          11       0.84      0.73      0.78        99
+          12       0.84      0.78      0.81        94
+          13       0.97      0.95      0.96        97
+          14       0.97      0.85      0.91       102
+          15       0.96      0.81      0.88        91
+          16       0.69      0.91      0.79       110
+    accuracy                           0.88      1700
+   macro avg       0.89      0.88      0.88      1700
+weighted avg       0.89      0.88      0.88      1700
 </t>
         </is>
       </c>
@@ -518,10 +518,10 @@
         <v>144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9673</v>
+        <v>0.9911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="3">
@@ -530,41 +530,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'svc_rbf__C': 10, 'svc_rbf__gamma': 0.001, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
+          <t>{'svc_rbf__C': 1, 'svc_rbf__gamma': 0.001, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.9335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9816</v>
+        <v>0.9972</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5541</v>
+        <v>3.2682</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.85      0.99      0.92        99
-           1       0.63      0.66      0.65       104
-           2       0.69      0.73      0.71       112
-           3       0.84      0.93      0.88        86
-           4       0.75      0.69      0.72        88
-           5       0.79      0.77      0.78        98
-           6       0.92      0.94      0.93       101
-           7       0.77      0.67      0.72        94
-           8       0.68      0.64      0.66        99
-           9       0.99      1.00      1.00       105
-          10       0.90      0.86      0.88       121
-          11       0.63      0.58      0.60        99
-          12       0.68      0.67      0.68        94
+           0       0.99      1.00      0.99        99
+           1       0.93      0.97      0.95       104
+           2       0.98      0.99      0.99       112
+           3       1.00      0.97      0.98        86
+           4       0.93      0.93      0.93        88
+           5       0.95      0.93      0.94        98
+           6       0.98      0.91      0.94       101
+           7       0.99      0.86      0.92        94
+           8       0.82      0.91      0.86        99
+           9       1.00      1.00      1.00       105
+          10       0.97      0.98      0.98       121
+          11       0.97      0.85      0.90        99
+          12       0.69      0.87      0.77        94
           13       0.99      1.00      0.99        97
-          14       0.54      0.42      0.47       102
-          15       0.79      0.63      0.70        91
-          16       0.68      0.95      0.79       110
-    accuracy                           0.77      1700
-   macro avg       0.77      0.77      0.77      1700
-weighted avg       0.77      0.77      0.77      1700
+          14       1.00      0.93      0.96       102
+          15       0.92      0.77      0.84        91
+          16       0.86      0.95      0.91       110
+    accuracy                           0.93      1700
+   macro avg       0.94      0.93      0.93      1700
+weighted avg       0.94      0.93      0.93      1700
 </t>
         </is>
       </c>
@@ -572,10 +572,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9792</v>
+        <v>0.9963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="4">
@@ -588,37 +588,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7694</v>
+        <v>0.9341</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9823</v>
+        <v>0.9974</v>
       </c>
       <c r="E4" t="n">
-        <v>17.8553</v>
+        <v>4.7324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.80      0.99      0.89        99
-           1       0.57      0.58      0.57       104
-           2       0.63      0.60      0.61       112
-           3       0.79      0.94      0.86        86
-           4       0.74      0.78      0.76        88
-           5       0.80      0.78      0.79        98
-           6       0.89      0.92      0.91       101
-           7       0.80      0.70      0.75        94
-           8       0.77      0.76      0.76        99
+           0       0.97      1.00      0.99        99
+           1       0.96      0.85      0.90       104
+           2       0.97      0.99      0.98       112
+           3       0.99      1.00      0.99        86
+           4       0.95      0.99      0.97        88
+           5       0.98      0.96      0.97        98
+           6       0.91      0.94      0.93       101
+           7       0.99      0.76      0.86        94
+           8       0.80      0.91      0.85        99
            9       0.99      1.00      1.00       105
-          10       0.80      0.79      0.79       121
-          11       0.68      0.51      0.58        99
-          12       0.93      0.73      0.82        94
-          13       0.98      1.00      0.99        97
-          14       0.46      0.40      0.43       102
-          15       0.86      0.73      0.79        91
-          16       0.65      0.91      0.75       110
-    accuracy                           0.77      1700
-   macro avg       0.77      0.77      0.77      1700
-weighted avg       0.77      0.77      0.77      1700
+          10       0.95      0.93      0.94       121
+          11       0.93      0.94      0.93        99
+          12       0.96      0.85      0.90        94
+          13       0.99      1.00      0.99        97
+          14       1.00      0.95      0.97       102
+          15       0.95      0.88      0.91        91
+          16       0.72      0.94      0.81       110
+    accuracy                           0.93      1700
+   macro avg       0.94      0.93      0.94      1700
+weighted avg       0.94      0.93      0.93      1700
 </t>
         </is>
       </c>
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9822</v>
+        <v>0.9971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
@@ -476,41 +476,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'identity', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (15, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
+          <t>{'mlp__activation': 'logistic', 'mlp__alpha': 0.001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9932</v>
+        <v>0.9425</v>
       </c>
       <c r="E2" t="n">
-        <v>8.812900000000001</v>
+        <v>36.3588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.99      0.99      0.99        99
-           1       0.60      0.82      0.69       104
-           2       0.96      0.97      0.97       112
-           3       0.95      1.00      0.97        86
-           4       0.90      0.95      0.93        88
-           5       0.92      0.95      0.93        98
-           6       0.82      0.86      0.84       101
-           7       0.96      0.70      0.81        94
-           8       0.84      0.85      0.84        99
-           9       0.99      1.00      1.00       105
-          10       0.93      0.79      0.85       121
-          11       0.84      0.73      0.78        99
-          12       0.84      0.78      0.81        94
-          13       0.97      0.95      0.96        97
-          14       0.97      0.85      0.91       102
-          15       0.96      0.81      0.88        91
-          16       0.69      0.91      0.79       110
-    accuracy                           0.88      1700
-   macro avg       0.89      0.88      0.88      1700
-weighted avg       0.89      0.88      0.88      1700
+           0       0.56      0.85      0.68        99
+           1       0.40      0.40      0.40       104
+           2       0.45      0.31      0.37       112
+           3       0.52      0.80      0.63        86
+           4       0.40      0.62      0.48        88
+           5       0.50      0.71      0.59        98
+           6       0.57      0.92      0.70       101
+           7       0.24      0.10      0.14        94
+           8       0.46      0.22      0.30        99
+           9       0.94      1.00      0.97       105
+          10       0.74      0.62      0.68       121
+          11       0.62      0.20      0.31        99
+          12       0.29      0.31      0.30        94
+          13       0.52      0.67      0.59        97
+          14       0.52      0.46      0.49       102
+          15       0.32      0.09      0.14        91
+          16       0.46      0.53      0.49       110
+    accuracy                           0.52      1700
+   macro avg       0.50      0.52      0.49      1700
+weighted avg       0.51      0.52      0.49      1700
 </t>
         </is>
       </c>
@@ -518,10 +518,10 @@
         <v>144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9911</v>
+        <v>0.9331</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="3">
@@ -534,37 +534,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9335</v>
+        <v>0.5553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9972</v>
+        <v>0.9434</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2682</v>
+        <v>25.4712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.99      1.00      0.99        99
-           1       0.93      0.97      0.95       104
-           2       0.98      0.99      0.99       112
-           3       1.00      0.97      0.98        86
-           4       0.93      0.93      0.93        88
-           5       0.95      0.93      0.94        98
-           6       0.98      0.91      0.94       101
-           7       0.99      0.86      0.92        94
-           8       0.82      0.91      0.86        99
-           9       1.00      1.00      1.00       105
-          10       0.97      0.98      0.98       121
-          11       0.97      0.85      0.90        99
-          12       0.69      0.87      0.77        94
-          13       0.99      1.00      0.99        97
-          14       1.00      0.93      0.96       102
-          15       0.92      0.77      0.84        91
-          16       0.86      0.95      0.91       110
-    accuracy                           0.93      1700
-   macro avg       0.94      0.93      0.93      1700
-weighted avg       0.94      0.93      0.93      1700
+           0       0.90      0.95      0.92        99
+           1       0.59      0.37      0.45       104
+           2       0.80      0.56      0.66       112
+           3       0.55      0.42      0.47        86
+           4       0.54      0.40      0.46        88
+           5       0.55      0.37      0.44        98
+           6       0.95      0.78      0.86       101
+           7       0.43      0.28      0.34        94
+           8       0.44      0.16      0.24        99
+           9       0.99      1.00      1.00       105
+          10       0.94      0.68      0.79       121
+          11       0.48      0.26      0.34        99
+          12       0.17      0.81      0.29        94
+          13       0.80      0.85      0.82        97
+          14       0.59      0.41      0.49       102
+          15       0.37      0.25      0.30        91
+          16       0.55      0.77      0.64       110
+    accuracy                           0.56      1700
+   macro avg       0.63      0.55      0.56      1700
+weighted avg       0.64      0.56      0.57      1700
 </t>
         </is>
       </c>
@@ -572,10 +572,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9963</v>
+        <v>0.9375</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0011</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="4">
@@ -588,37 +588,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9341</v>
+        <v>0.4859</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9974</v>
+        <v>0.9416</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7324</v>
+        <v>41.9194</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.97      1.00      0.99        99
-           1       0.96      0.85      0.90       104
-           2       0.97      0.99      0.98       112
-           3       0.99      1.00      0.99        86
-           4       0.95      0.99      0.97        88
-           5       0.98      0.96      0.97        98
-           6       0.91      0.94      0.93       101
-           7       0.99      0.76      0.86        94
-           8       0.80      0.91      0.85        99
-           9       0.99      1.00      1.00       105
-          10       0.95      0.93      0.94       121
-          11       0.93      0.94      0.93        99
-          12       0.96      0.85      0.90        94
-          13       0.99      1.00      0.99        97
-          14       1.00      0.95      0.97       102
-          15       0.95      0.88      0.91        91
-          16       0.72      0.94      0.81       110
-    accuracy                           0.93      1700
-   macro avg       0.94      0.93      0.94      1700
-weighted avg       0.94      0.93      0.93      1700
+           0       0.32      0.42      0.36        99
+           1       0.52      0.31      0.39       104
+           2       0.56      0.35      0.43       112
+           3       0.32      0.81      0.46        86
+           4       0.46      0.69      0.55        88
+           5       0.45      0.61      0.52        98
+           6       0.85      0.85      0.85       101
+           7       0.28      0.35      0.31        94
+           8       0.74      0.25      0.38        99
+           9       0.78      1.00      0.88       105
+          10       0.68      0.45      0.54       121
+          11       0.55      0.27      0.36        99
+          12       0.82      0.38      0.52        94
+          13       0.67      0.37      0.48        97
+          14       0.49      0.47      0.48       102
+          15       0.68      0.14      0.24        91
+          16       0.26      0.53      0.35       110
+    accuracy                           0.49      1700
+   macro avg       0.56      0.49      0.48      1700
+weighted avg       0.56      0.49      0.48      1700
 </t>
         </is>
       </c>
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9971</v>
+        <v>0.9391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005</v>
+        <v>0.0043</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
@@ -475,45 +475,45 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5044</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>34.52</v>
+        <v>33.3541</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        18
-           1       0.00      0.00      0.00        29
-           2       0.00      0.00      0.00        21
-           3       0.00      0.00      0.00        25
-           4       0.00      0.00      0.00        18
-           5       0.07      1.00      0.13        30
-           6       0.00      0.00      0.00        29
-           7       0.00      0.00      0.00        28
-           8       0.00      0.00      0.00        24
-           9       0.00      0.00      0.00        16
-          10       0.00      0.00      0.00        31
-          11       0.00      0.00      0.00        24
-          12       0.00      0.00      0.00        26
-          13       0.00      0.00      0.00        23
-          14       0.00      0.00      0.00        31
-          15       0.14      0.03      0.05        31
-          16       0.00      0.00      0.00        21
-    accuracy                           0.07       425
-   macro avg       0.01      0.06      0.01       425
-weighted avg       0.02      0.07      0.01       425
+           0       0.00      0.00      0.00        99
+           1       0.00      0.00      0.00       104
+           2       0.00      0.00      0.00       112
+           3       0.00      0.00      0.00        86
+           4       0.00      0.00      0.00        88
+           5       0.06      1.00      0.11        98
+           6       0.00      0.00      0.00       101
+           7       0.00      0.00      0.00        94
+           8       0.00      0.00      0.00        99
+           9       0.00      0.00      0.00       105
+          10       0.00      0.00      0.00       121
+          11       0.00      0.00      0.00        99
+          12       0.00      0.00      0.00        94
+          13       0.00      0.00      0.00        97
+          14       0.00      0.00      0.00       102
+          15       0.00      0.00      0.00        91
+          16       0.00      0.00      0.00       110
+    accuracy                           0.06      1700
+   macro avg       0.00      0.06      0.01      1700
+weighted avg       0.00      0.06      0.01      1700
 </t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0567</v>
+        <v>0.0589</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0045</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="3">
@@ -526,45 +526,45 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0518</v>
+        <v>0.1059</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5128</v>
+        <v>0.6435</v>
       </c>
       <c r="E3" t="n">
-        <v>80.0094</v>
+        <v>52.0182</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.04      0.78      0.08        18
-           1       0.25      0.03      0.06        29
-           2       0.00      0.00      0.00        21
-           3       0.00      0.00      0.00        25
-           4       0.05      0.06      0.05        18
-           5       0.00      0.00      0.00        30
-           6       0.00      0.00      0.00        29
-           7       0.00      0.00      0.00        28
-           8       0.08      0.04      0.06        24
-           9       0.07      0.06      0.07        16
-          10       0.50      0.06      0.11        31
-          11       0.00      0.00      0.00        24
-          12       0.25      0.04      0.07        26
-          13       0.00      0.00      0.00        23
-          14       0.00      0.00      0.00        31
-          15       0.00      0.00      0.00        31
-          16       0.11      0.05      0.07        21
-    accuracy                           0.05       425
-   macro avg       0.08      0.07      0.03       425
-weighted avg       0.09      0.05      0.03       425
+           0       0.10      0.07      0.08        99
+           1       0.25      0.13      0.17       104
+           2       0.17      0.05      0.08       112
+           3       0.09      0.10      0.09        86
+           4       0.12      0.14      0.13        88
+           5       0.11      0.05      0.07        98
+           6       0.31      0.21      0.25       101
+           7       0.07      0.06      0.07        94
+           8       0.05      0.04      0.05        99
+           9       0.16      0.09      0.11       105
+          10       0.21      0.05      0.08       121
+          11       0.06      0.04      0.05        99
+          12       0.13      0.11      0.12        94
+          13       0.17      0.09      0.12        97
+          14       0.05      0.02      0.03       102
+          15       0.07      0.54      0.13        91
+          16       0.11      0.06      0.08       110
+    accuracy                           0.11      1700
+   macro avg       0.13      0.11      0.10      1700
+weighted avg       0.13      0.11      0.10      1700
 </t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.064</v>
+        <v>0.0965</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="4">
@@ -577,45 +577,45 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0376</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5205</v>
+        <v>0.6808</v>
       </c>
       <c r="E4" t="n">
-        <v>24.0447</v>
+        <v>48.8824</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        18
-           1       0.00      0.00      0.00        29
-           2       0.00      0.00      0.00        21
-           3       0.00      0.00      0.00        25
-           4       0.00      0.00      0.00        18
-           5       0.00      0.00      0.00        30
-           6       0.00      0.00      0.00        29
-           7       0.00      0.00      0.00        28
-           8       0.00      0.00      0.00        24
-           9       0.04      1.00      0.07        16
-          10       0.00      0.00      0.00        31
-          11       0.00      0.00      0.00        24
-          12       0.00      0.00      0.00        26
-          13       0.00      0.00      0.00        23
-          14       0.00      0.00      0.00        31
-          15       0.00      0.00      0.00        31
-          16       0.00      0.00      0.00        21
-    accuracy                           0.04       425
-   macro avg       0.00      0.06      0.00       425
-weighted avg       0.00      0.04      0.00       425
+           0       0.00      0.00      0.00        99
+           1       0.00      0.00      0.00       104
+           2       0.00      0.00      0.00       112
+           3       0.05      0.99      0.10        86
+           4       0.32      0.09      0.14        88
+           5       0.00      0.00      0.00        98
+           6       0.40      0.17      0.24       101
+           7       0.00      0.00      0.00        94
+           8       0.00      0.00      0.00        99
+           9       0.00      0.00      0.00       105
+          10       0.00      0.00      0.00       121
+          11       0.00      0.00      0.00        99
+          12       0.00      0.00      0.00        94
+          13       0.00      0.00      0.00        97
+          14       0.00      0.00      0.00       102
+          15       0.00      0.00      0.00        91
+          16       0.00      0.00      0.00       110
+    accuracy                           0.06      1700
+   macro avg       0.05      0.07      0.03      1700
+weighted avg       0.04      0.06      0.03      1700
 </t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.0625</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0036</v>
+        <v>0.0053</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,121 +471,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.01, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'sgd'}</t>
+          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0576</v>
+        <v>0.0559</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.5049</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3541</v>
+        <v>49.2488</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        99
-           1       0.00      0.00      0.00       104
-           2       0.00      0.00      0.00       112
-           3       0.00      0.00      0.00        86
-           4       0.00      0.00      0.00        88
-           5       0.06      1.00      0.11        98
-           6       0.00      0.00      0.00       101
-           7       0.00      0.00      0.00        94
-           8       0.00      0.00      0.00        99
-           9       0.00      0.00      0.00       105
-          10       0.00      0.00      0.00       121
-          11       0.00      0.00      0.00        99
-          12       0.00      0.00      0.00        94
-          13       0.00      0.00      0.00        97
-          14       0.00      0.00      0.00       102
-          15       0.00      0.00      0.00        91
-          16       0.00      0.00      0.00       110
-    accuracy                           0.06      1700
-   macro avg       0.00      0.06      0.01      1700
-weighted avg       0.00      0.06      0.01      1700
-</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'svc_rbf__C': 1, 'svc_rbf__gamma': 0.01, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.5904</v>
-      </c>
-      <c r="E3" t="n">
-        <v>48.4794</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.37      0.07      0.12        99
-           1       0.14      0.02      0.03       104
-           2       0.10      0.01      0.02       112
-           3       0.05      0.91      0.10        86
-           4       0.13      0.06      0.08        88
-           5       0.00      0.00      0.00        98
-           6       1.00      0.03      0.06       101
-           7       0.11      0.02      0.04        94
-           8       0.09      0.01      0.02        99
-           9       0.81      0.21      0.33       105
-          10       1.00      0.01      0.02       121
-          11       0.11      0.01      0.02        99
-          12       0.20      0.01      0.02        94
-          13       0.24      0.04      0.07        97
-          14       0.00      0.00      0.00       102
-          15       0.12      0.01      0.02        91
-          16       0.24      0.04      0.06       110
-    accuracy                           0.08      1700
-   macro avg       0.28      0.09      0.06      1700
-weighted avg       0.29      0.08      0.06      1700
-</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0814</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'qsvc__probability': True}</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0559</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5109</v>
-      </c>
-      <c r="E4" t="n">
-        <v>49.2488</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
            0       0.00      0.00      0.00        99
@@ -611,10 +509,10 @@
 </t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G2" t="n">
         <v>0.0648</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H2" t="n">
         <v>0.0026</v>
       </c>
     </row>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_reconstructed_random.xlsx
@@ -425,43 +425,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>melhores_parametros</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>acuracia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>roc_auc_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mse</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>relatorio_classificacao</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>best_mean_score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>std_best_score_k_fold</t>
         </is>
       </c>
     </row>
@@ -469,51 +454,40 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.0853</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0559</v>
+        <v>0.5966</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5049</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.2488</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>38.0294</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
            0       0.00      0.00      0.00        99
            1       0.00      0.00      0.00       104
-           2       0.00      0.00      0.00       112
-           3       0.05      0.98      0.10        86
-           4       0.00      0.00      0.00        88
-           5       0.00      0.00      0.00        98
-           6       0.40      0.08      0.13       101
-           7       0.00      0.00      0.00        94
-           8       1.00      0.01      0.02        99
-           9       0.00      0.00      0.00       105
+           2       0.21      0.26      0.23       112
+           3       0.00      0.00      0.00        86
+           4       0.05      0.02      0.03        88
+           5       0.06      0.01      0.02        98
+           6       0.00      0.00      0.00       101
+           7       0.27      0.03      0.06        94
+           8       0.02      0.01      0.01        99
+           9       0.12      0.10      0.11       105
           10       0.00      0.00      0.00       121
-          11       0.00      0.00      0.00        99
-          12       0.00      0.00      0.00        94
-          13       0.00      0.00      0.00        97
-          14       0.00      0.00      0.00       102
-          15       0.29      0.02      0.04        91
+          11       0.07      0.90      0.13        99
+          12       0.09      0.02      0.03        94
+          13       0.14      0.01      0.02        97
+          14       0.28      0.05      0.08       102
+          15       0.09      0.02      0.04        91
           16       0.00      0.00      0.00       110
-    accuracy                           0.06      1700
-   macro avg       0.10      0.06      0.02      1700
-weighted avg       0.10      0.06      0.02      1700
+    accuracy                           0.09      1700
+   macro avg       0.08      0.08      0.04      1700
+weighted avg       0.08      0.09      0.05      1700
 </t>
         </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0026</v>
       </c>
     </row>
   </sheetData>
